--- a/diseases/d006/2020-2025.xlsx
+++ b/diseases/d006/2020-2025.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -35641,7 +35641,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -37723,7 +37723,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -38690,7 +38690,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -41739,7 +41739,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -42706,7 +42706,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -43821,7 +43821,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -44788,7 +44788,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -47837,7 +47837,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49919,7 +49919,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -50886,7 +50886,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -51853,7 +51853,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -52968,7 +52968,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -55050,7 +55050,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -56017,7 +56017,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -56984,7 +56984,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -58099,7 +58099,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -59066,7 +59066,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -61148,7 +61148,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -62115,7 +62115,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -63230,7 +63230,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -64197,7 +64197,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -65164,7 +65164,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -66131,7 +66131,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
@@ -67246,7 +67246,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -68213,7 +68213,7 @@
       </c>
       <c r="AJ422" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK422" t="inlineStr">
@@ -69180,7 +69180,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -70295,7 +70295,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -71262,7 +71262,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -72377,7 +72377,7 @@
       </c>
       <c r="AJ448" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK448" t="inlineStr">
@@ -73344,7 +73344,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">

--- a/diseases/d006/2020-2025.xlsx
+++ b/diseases/d006/2020-2025.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -35641,7 +35641,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -37723,7 +37723,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -38690,7 +38690,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -41739,7 +41739,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -42706,7 +42706,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -43821,7 +43821,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -44788,7 +44788,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -47837,7 +47837,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49919,7 +49919,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -50886,7 +50886,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -51853,7 +51853,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -52968,7 +52968,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -55050,7 +55050,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -56017,7 +56017,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -56984,7 +56984,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -58099,7 +58099,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -59066,7 +59066,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -61148,7 +61148,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -62115,7 +62115,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -63230,7 +63230,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -64197,7 +64197,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -65164,7 +65164,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -66131,7 +66131,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
@@ -67246,7 +67246,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -68213,7 +68213,7 @@
       </c>
       <c r="AJ422" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK422" t="inlineStr">
@@ -69180,7 +69180,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -70295,7 +70295,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -71262,7 +71262,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -72377,7 +72377,7 @@
       </c>
       <c r="AJ448" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK448" t="inlineStr">
@@ -73344,7 +73344,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">

--- a/diseases/d006/2020-2025.xlsx
+++ b/diseases/d006/2020-2025.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -35641,7 +35641,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -37723,7 +37723,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -38690,7 +38690,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -41739,7 +41739,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -42706,7 +42706,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -43821,7 +43821,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -44788,7 +44788,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -47837,7 +47837,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49919,7 +49919,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -50886,7 +50886,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -51853,7 +51853,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -52968,7 +52968,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -55050,7 +55050,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -56017,7 +56017,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -56984,7 +56984,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -58099,7 +58099,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -59066,7 +59066,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -61148,7 +61148,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -62115,7 +62115,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -63230,7 +63230,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -64197,7 +64197,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -65164,7 +65164,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -66131,7 +66131,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
@@ -67246,7 +67246,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -68213,7 +68213,7 @@
       </c>
       <c r="AJ422" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK422" t="inlineStr">
@@ -69180,7 +69180,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -70295,7 +70295,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -71262,7 +71262,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -72377,7 +72377,7 @@
       </c>
       <c r="AJ448" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK448" t="inlineStr">
@@ -73344,7 +73344,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">

--- a/diseases/d006/2020-2025.xlsx
+++ b/diseases/d006/2020-2025.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -35641,7 +35641,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -37723,7 +37723,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -38690,7 +38690,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -41739,7 +41739,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -42706,7 +42706,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -43821,7 +43821,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -44788,7 +44788,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -47837,7 +47837,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49919,7 +49919,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -50886,7 +50886,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -51853,7 +51853,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -52968,7 +52968,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -55050,7 +55050,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -56017,7 +56017,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -56984,7 +56984,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -58099,7 +58099,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -59066,7 +59066,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -61148,7 +61148,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -62115,7 +62115,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -63230,7 +63230,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -64197,7 +64197,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -65164,7 +65164,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -66131,7 +66131,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
@@ -67246,7 +67246,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -68213,7 +68213,7 @@
       </c>
       <c r="AJ422" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK422" t="inlineStr">
@@ -69180,7 +69180,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -70295,7 +70295,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -71262,7 +71262,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -72377,7 +72377,7 @@
       </c>
       <c r="AJ448" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK448" t="inlineStr">
@@ -73344,7 +73344,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">

--- a/diseases/d006/2020-2025.xlsx
+++ b/diseases/d006/2020-2025.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -35641,7 +35641,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -37723,7 +37723,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -38690,7 +38690,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -41739,7 +41739,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -42706,7 +42706,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -43821,7 +43821,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -44788,7 +44788,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -47837,7 +47837,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -49919,7 +49919,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -50886,7 +50886,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -51853,7 +51853,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -52968,7 +52968,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -55050,7 +55050,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -56017,7 +56017,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -56984,7 +56984,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -58099,7 +58099,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -59066,7 +59066,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -61148,7 +61148,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -62115,7 +62115,7 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
@@ -63230,7 +63230,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -64197,7 +64197,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -65164,7 +65164,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -66131,7 +66131,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
@@ -67246,7 +67246,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -68213,7 +68213,7 @@
       </c>
       <c r="AJ422" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK422" t="inlineStr">
@@ -69180,7 +69180,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -70295,7 +70295,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -71262,7 +71262,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -72377,7 +72377,7 @@
       </c>
       <c r="AJ448" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK448" t="inlineStr">
@@ -73344,7 +73344,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">
